--- a/iatf_system/lib/excel_templates/process_design_plan_report_modified.xlsx
+++ b/iatf_system/lib/excel_templates/process_design_plan_report_modified.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\document_production_minipc_only_npm_20250208\lib\excel_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271E2BB0-06AC-4FFD-9147-E6975D1B29B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,101 +35,101 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
     <author>mhin25</author>
   </authors>
   <commentList>
-    <comment ref="M13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="M13" authorId="0">
       <text>
         <r>
           <rPr>
-            <b/>
+            <rFont val="MS P ゴシック"/>
+            <charset val="128"/>
+            <family val="3"/>
+            <b val="1"/>
+            <color indexed="81"/>
             <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
           </rPr>
           <t>設計計画書　基本設計完了日</t>
         </r>
       </text>
     </comment>
-    <comment ref="D31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="D31" authorId="0">
       <text>
         <r>
           <rPr>
-            <b/>
+            <rFont val="MS P ゴシック"/>
+            <charset val="128"/>
+            <family val="3"/>
+            <b val="1"/>
+            <color indexed="81"/>
             <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
           </rPr>
           <t>仕入先検査成績書</t>
         </r>
       </text>
     </comment>
-    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="D58" authorId="0">
       <text>
         <r>
           <rPr>
-            <b/>
+            <rFont val="MS P ゴシック"/>
+            <charset val="128"/>
+            <family val="3"/>
+            <b val="1"/>
+            <color indexed="81"/>
             <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
           </rPr>
-          <t>CP：
+          <t xml:space="preserve">CP：
 コントロールプラン</t>
         </r>
       </text>
     </comment>
-    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="D59" authorId="0">
       <text>
         <r>
           <rPr>
-            <b/>
+            <rFont val="MS P ゴシック"/>
+            <charset val="128"/>
+            <family val="3"/>
+            <b val="1"/>
+            <color indexed="81"/>
             <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
           </rPr>
-          <t>CP：
+          <t xml:space="preserve">CP：
 コントロールプラン</t>
         </r>
       </text>
     </comment>
-    <comment ref="D84" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="D84" authorId="0">
       <text>
         <r>
           <rPr>
-            <b/>
+            <rFont val="MS P ゴシック"/>
+            <charset val="128"/>
+            <family val="3"/>
+            <b val="1"/>
+            <color indexed="81"/>
             <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
           </rPr>
-          <t>CP：
+          <t xml:space="preserve">CP：
 コントロールプラン</t>
         </r>
       </text>
     </comment>
-    <comment ref="D87" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="D87" authorId="0">
       <text>
         <r>
           <rPr>
-            <b/>
+            <rFont val="MS P ゴシック"/>
+            <charset val="128"/>
+            <family val="3"/>
+            <b val="1"/>
+            <color indexed="81"/>
             <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
           </rPr>
-          <t>CP：
+          <t xml:space="preserve">CP：
 コントロールプラン</t>
         </r>
       </text>
@@ -140,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="314" count="314">
   <si>
     <t>段階</t>
     <rPh sb="0" eb="2">
@@ -613,11 +612,11 @@
     </r>
     <r>
       <rPr>
-        <b/>
+        <rFont val="ＭＳ Ｐ明朝"/>
+        <charset val="128"/>
+        <family val="1"/>
+        <b val="1"/>
         <sz val="9"/>
-        <rFont val="ＭＳ Ｐ明朝"/>
-        <family val="1"/>
-        <charset val="128"/>
       </rPr>
       <t>検証(確認・承認)</t>
     </r>
@@ -700,11 +699,11 @@
     </r>
     <r>
       <rPr>
-        <b/>
+        <rFont val="ＭＳ Ｐ明朝"/>
+        <charset val="128"/>
+        <family val="1"/>
+        <b val="1"/>
         <sz val="9"/>
-        <rFont val="ＭＳ Ｐ明朝"/>
-        <family val="1"/>
-        <charset val="128"/>
       </rPr>
       <t>確認/試作ﾌﾟﾛｸﾞﾗﾑ/製品承認ﾌﾟﾛｾｽ</t>
     </r>
@@ -1191,7 +1190,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ｲﾝﾀｰﾌｪｰｽ
+    <t xml:space="preserve">ｲﾝﾀｰﾌｪｰｽ
 部門</t>
     <rPh sb="9" eb="11">
       <t>ブモン</t>
@@ -1874,7 +1873,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>設備名：#{?dr_setsubi_name_1}
+    <t xml:space="preserve">設備名：#{?dr_setsubi_name_1}
 #{?dr_setsubi_shiteki_1}</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1934,7 +1933,7 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>項番：#{?grr_no_1}
+    <t xml:space="preserve">項番：#{?grr_no_1}
 GRR値：#{?grr_1}、GRR結果：#{?grr_result_1}
 ndc値：#{?ndc_1}、ndc結果：#{?ndc_result_1}</t>
     <rPh sb="0" eb="2">
@@ -2357,7 +2356,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>#{?processflow_stamping_person_in_charge}
+    <t xml:space="preserve">#{?processflow_stamping_person_in_charge}
 #{?processflow_mold_person_in_charge}</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2445,7 +2444,7 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>(コメント)
+    <t xml:space="preserve">(コメント)
 問題なし。</t>
     <rPh sb="7" eb="9">
       <t>モンダイ</t>
@@ -2457,12 +2456,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>(コメント)
+    <t xml:space="preserve">(コメント)
 問題なし。</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>(コメント)
+    <t xml:space="preserve">(コメント)
 問題なし。</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -2481,140 +2480,140 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <fonts count="20">
     <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="2"/>
       <sz val="6"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐ明朝"/>
+      <charset val="128"/>
+      <family val="1"/>
       <sz val="12"/>
-      <name val="ＭＳ Ｐ明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <name val="ＭＳ Ｐ明朝"/>
+      <charset val="128"/>
+      <family val="1"/>
+      <b val="1"/>
       <sz val="16"/>
-      <name val="ＭＳ Ｐ明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <name val="ＭＳ Ｐ明朝"/>
+      <charset val="128"/>
+      <family val="1"/>
+      <b val="1"/>
       <sz val="10"/>
-      <name val="ＭＳ Ｐ明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐ明朝"/>
+      <charset val="128"/>
+      <family val="1"/>
       <sz val="10"/>
-      <name val="ＭＳ Ｐ明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐ明朝"/>
+      <charset val="128"/>
+      <family val="1"/>
       <sz val="11"/>
-      <name val="ＭＳ Ｐ明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐ明朝"/>
+      <charset val="128"/>
+      <family val="1"/>
       <sz val="9"/>
-      <name val="ＭＳ Ｐ明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <sz val="10"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <name val="ＭＳ Ｐ明朝"/>
+      <charset val="128"/>
+      <family val="1"/>
+      <b val="1"/>
       <sz val="9"/>
-      <name val="ＭＳ Ｐ明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
     </font>
     <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="8"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="8"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="ＭＳ Ｐ明朝"/>
+      <charset val="128"/>
+      <family val="1"/>
+      <b val="1"/>
       <sz val="18"/>
-      <name val="ＭＳ Ｐ明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <name val="MS P ゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color indexed="81"/>
       <sz val="9"/>
-      <color indexed="81"/>
-      <name val="MS P ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="Consolas"/>
       <family val="3"/>
+      <sz val="12"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐ明朝"/>
+      <charset val="128"/>
+      <family val="1"/>
+      <color theme="1"/>
       <sz val="8"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐ明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐ明朝"/>
+      <charset val="128"/>
+      <family val="1"/>
       <sz val="8"/>
-      <name val="ＭＳ Ｐ明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2626,7 +2625,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4226,7 +4225,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16" count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -4380,7 +4379,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -4406,7 +4405,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -4441,7 +4440,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -4484,7 +4483,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -4500,7 +4499,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Z103"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -4635,7 +4634,7 @@
     <col min="16119" max="16142" width="3.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14.25" customHeight="1">
+    <row r="1" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A1" s="60" t="s">
         <v>304</v>
       </c>
@@ -4665,7 +4664,7 @@
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
     </row>
-    <row r="2" spans="1:26" ht="14.25" customHeight="1">
+    <row r="2" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A2" s="113" t="s">
         <v>120</v>
       </c>
@@ -4697,7 +4696,7 @@
       <c r="Y2" s="53"/>
       <c r="Z2" s="112"/>
     </row>
-    <row r="3" spans="1:26" ht="14.25" customHeight="1">
+    <row r="3" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A3" s="115"/>
       <c r="B3" s="116"/>
       <c r="C3" s="116"/>
@@ -4735,7 +4734,7 @@
       <c r="Y3" s="100"/>
       <c r="Z3" s="101"/>
     </row>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1">
+    <row r="4" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A4" s="14" t="s">
         <v>118</v>
       </c>
@@ -4783,7 +4782,7 @@
       <c r="Y4" s="124"/>
       <c r="Z4" s="125"/>
     </row>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1" thickBot="1">
+    <row r="5" spans="1:26" customFormat="false" ht="14.25" customHeight="1" thickBot="1">
       <c r="A5" s="118" t="s">
         <v>146</v>
       </c>
@@ -4813,7 +4812,7 @@
       <c r="Y5" s="127"/>
       <c r="Z5" s="128"/>
     </row>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1">
+    <row r="6" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>0</v>
       </c>
@@ -4855,7 +4854,7 @@
       <c r="Y6" s="62"/>
       <c r="Z6" s="63"/>
     </row>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1">
+    <row r="7" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A7" s="36" t="s">
         <v>6</v>
       </c>
@@ -4897,7 +4896,7 @@
       </c>
       <c r="Z7" s="111"/>
     </row>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1">
+    <row r="8" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A8" s="37"/>
       <c r="B8" s="68" t="s">
         <v>115</v>
@@ -4947,7 +4946,7 @@
       </c>
       <c r="Z8" s="184"/>
     </row>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1">
+    <row r="9" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A9" s="37"/>
       <c r="B9" s="71"/>
       <c r="C9" s="72"/>
@@ -4992,7 +4991,7 @@
       </c>
       <c r="Z9" s="243"/>
     </row>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1">
+    <row r="10" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A10" s="37"/>
       <c r="B10" s="74"/>
       <c r="C10" s="75"/>
@@ -5022,7 +5021,7 @@
       <c r="Y10" s="242"/>
       <c r="Z10" s="243"/>
     </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1">
+    <row r="11" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A11" s="37"/>
       <c r="B11" s="325" t="s">
         <v>10</v>
@@ -5058,7 +5057,7 @@
       <c r="Y11" s="242"/>
       <c r="Z11" s="243"/>
     </row>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1">
+    <row r="12" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A12" s="37"/>
       <c r="B12" s="326"/>
       <c r="C12" s="169"/>
@@ -5092,7 +5091,7 @@
       <c r="Y12" s="242"/>
       <c r="Z12" s="243"/>
     </row>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1">
+    <row r="13" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A13" s="37"/>
       <c r="B13" s="326"/>
       <c r="C13" s="38" t="s">
@@ -5132,7 +5131,7 @@
       <c r="Y13" s="242"/>
       <c r="Z13" s="243"/>
     </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1">
+    <row r="14" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A14" s="37"/>
       <c r="B14" s="326"/>
       <c r="C14" s="39"/>
@@ -5162,7 +5161,7 @@
       <c r="Y14" s="242"/>
       <c r="Z14" s="243"/>
     </row>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1">
+    <row r="15" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A15" s="37"/>
       <c r="B15" s="326"/>
       <c r="C15" s="39"/>
@@ -5202,7 +5201,7 @@
       <c r="Y15" s="244"/>
       <c r="Z15" s="245"/>
     </row>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1">
+    <row r="16" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A16" s="37"/>
       <c r="B16" s="326"/>
       <c r="C16" s="39"/>
@@ -5242,7 +5241,7 @@
       </c>
       <c r="Z16" s="301"/>
     </row>
-    <row r="17" spans="1:26" ht="14.25" customHeight="1">
+    <row r="17" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A17" s="37"/>
       <c r="B17" s="326"/>
       <c r="C17" s="39"/>
@@ -5280,7 +5279,7 @@
       <c r="Y17" s="302"/>
       <c r="Z17" s="303"/>
     </row>
-    <row r="18" spans="1:26" ht="14.25" customHeight="1">
+    <row r="18" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A18" s="37"/>
       <c r="B18" s="326"/>
       <c r="C18" s="39"/>
@@ -5324,7 +5323,7 @@
       </c>
       <c r="Z18" s="184"/>
     </row>
-    <row r="19" spans="1:26" ht="14.25" customHeight="1">
+    <row r="19" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A19" s="37"/>
       <c r="B19" s="326"/>
       <c r="C19" s="39"/>
@@ -5368,7 +5367,7 @@
       </c>
       <c r="Z19" s="298"/>
     </row>
-    <row r="20" spans="1:26" ht="14.25" customHeight="1">
+    <row r="20" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A20" s="37"/>
       <c r="B20" s="326"/>
       <c r="C20" s="39"/>
@@ -5408,7 +5407,7 @@
       <c r="Y20" s="246"/>
       <c r="Z20" s="298"/>
     </row>
-    <row r="21" spans="1:26" ht="14.25" customHeight="1">
+    <row r="21" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A21" s="37"/>
       <c r="B21" s="326"/>
       <c r="C21" s="39"/>
@@ -5448,7 +5447,7 @@
       <c r="Y21" s="246"/>
       <c r="Z21" s="298"/>
     </row>
-    <row r="22" spans="1:26" ht="14.25" customHeight="1">
+    <row r="22" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A22" s="37"/>
       <c r="B22" s="326"/>
       <c r="C22" s="39"/>
@@ -5496,7 +5495,7 @@
       <c r="Y22" s="246"/>
       <c r="Z22" s="298"/>
     </row>
-    <row r="23" spans="1:26" ht="14.25" customHeight="1">
+    <row r="23" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A23" s="37"/>
       <c r="B23" s="326"/>
       <c r="C23" s="39"/>
@@ -5538,7 +5537,7 @@
       <c r="Y23" s="246"/>
       <c r="Z23" s="298"/>
     </row>
-    <row r="24" spans="1:26" ht="14.25" customHeight="1">
+    <row r="24" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A24" s="37"/>
       <c r="B24" s="326"/>
       <c r="C24" s="39"/>
@@ -5574,7 +5573,7 @@
       <c r="Y24" s="246"/>
       <c r="Z24" s="298"/>
     </row>
-    <row r="25" spans="1:26" ht="14.25" customHeight="1">
+    <row r="25" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A25" s="37"/>
       <c r="B25" s="326"/>
       <c r="C25" s="39"/>
@@ -5612,7 +5611,7 @@
       <c r="Y25" s="246"/>
       <c r="Z25" s="298"/>
     </row>
-    <row r="26" spans="1:26" ht="14.25" customHeight="1">
+    <row r="26" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A26" s="37"/>
       <c r="B26" s="326"/>
       <c r="C26" s="40"/>
@@ -5648,7 +5647,7 @@
       <c r="Y26" s="246"/>
       <c r="Z26" s="298"/>
     </row>
-    <row r="27" spans="1:26" ht="14.25" customHeight="1">
+    <row r="27" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A27" s="6" t="s">
         <v>27</v>
       </c>
@@ -5688,7 +5687,7 @@
       <c r="Y27" s="246"/>
       <c r="Z27" s="298"/>
     </row>
-    <row r="28" spans="1:26" ht="14.25" customHeight="1">
+    <row r="28" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A28" s="34" t="s">
         <v>313</v>
       </c>
@@ -5726,7 +5725,7 @@
       <c r="Y28" s="246"/>
       <c r="Z28" s="298"/>
     </row>
-    <row r="29" spans="1:26" ht="14.25" customHeight="1">
+    <row r="29" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A29" s="34"/>
       <c r="B29" s="326"/>
       <c r="C29" s="323"/>
@@ -5762,7 +5761,7 @@
       <c r="Y29" s="246"/>
       <c r="Z29" s="298"/>
     </row>
-    <row r="30" spans="1:26" ht="14.25" customHeight="1">
+    <row r="30" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A30" s="34"/>
       <c r="B30" s="326"/>
       <c r="C30" s="323"/>
@@ -5798,7 +5797,7 @@
       <c r="Y30" s="246"/>
       <c r="Z30" s="298"/>
     </row>
-    <row r="31" spans="1:26" ht="14.25" customHeight="1">
+    <row r="31" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A31" s="34"/>
       <c r="B31" s="326"/>
       <c r="C31" s="323"/>
@@ -5834,7 +5833,7 @@
       <c r="Y31" s="246"/>
       <c r="Z31" s="298"/>
     </row>
-    <row r="32" spans="1:26" ht="14.25" customHeight="1">
+    <row r="32" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A32" s="34"/>
       <c r="B32" s="326"/>
       <c r="C32" s="323"/>
@@ -5874,7 +5873,7 @@
       <c r="Y32" s="246"/>
       <c r="Z32" s="298"/>
     </row>
-    <row r="33" spans="1:26" ht="14.25" customHeight="1">
+    <row r="33" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A33" s="34"/>
       <c r="B33" s="326"/>
       <c r="C33" s="323"/>
@@ -5906,7 +5905,7 @@
       <c r="Y33" s="246"/>
       <c r="Z33" s="298"/>
     </row>
-    <row r="34" spans="1:26" ht="14.25" customHeight="1">
+    <row r="34" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A34" s="34"/>
       <c r="B34" s="326"/>
       <c r="C34" s="323"/>
@@ -5938,7 +5937,7 @@
       <c r="Y34" s="246"/>
       <c r="Z34" s="298"/>
     </row>
-    <row r="35" spans="1:26" ht="14.25" customHeight="1">
+    <row r="35" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A35" s="34"/>
       <c r="B35" s="326"/>
       <c r="C35" s="323"/>
@@ -5974,7 +5973,7 @@
       <c r="Y35" s="246"/>
       <c r="Z35" s="298"/>
     </row>
-    <row r="36" spans="1:26" ht="14.25" customHeight="1">
+    <row r="36" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A36" s="34"/>
       <c r="B36" s="326"/>
       <c r="C36" s="323"/>
@@ -6010,7 +6009,7 @@
       <c r="Y36" s="246"/>
       <c r="Z36" s="298"/>
     </row>
-    <row r="37" spans="1:26" ht="45" customHeight="1">
+    <row r="37" spans="1:26" customFormat="false" ht="45" customHeight="1">
       <c r="A37" s="34"/>
       <c r="B37" s="326"/>
       <c r="C37" s="323"/>
@@ -6048,7 +6047,7 @@
       <c r="Y37" s="246"/>
       <c r="Z37" s="298"/>
     </row>
-    <row r="38" spans="1:26" ht="14.25" customHeight="1">
+    <row r="38" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A38" s="34"/>
       <c r="B38" s="326"/>
       <c r="C38" s="323"/>
@@ -6086,7 +6085,7 @@
       <c r="Y38" s="246"/>
       <c r="Z38" s="298"/>
     </row>
-    <row r="39" spans="1:26" ht="14.25" customHeight="1">
+    <row r="39" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A39" s="34"/>
       <c r="B39" s="326"/>
       <c r="C39" s="323"/>
@@ -6122,7 +6121,7 @@
       <c r="Y39" s="246"/>
       <c r="Z39" s="298"/>
     </row>
-    <row r="40" spans="1:26" ht="14.25" customHeight="1">
+    <row r="40" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A40" s="34"/>
       <c r="B40" s="326"/>
       <c r="C40" s="323"/>
@@ -6158,7 +6157,7 @@
       <c r="Y40" s="246"/>
       <c r="Z40" s="298"/>
     </row>
-    <row r="41" spans="1:26" ht="14.25" customHeight="1">
+    <row r="41" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A41" s="34"/>
       <c r="B41" s="326"/>
       <c r="C41" s="323"/>
@@ -6194,7 +6193,7 @@
       <c r="Y41" s="246"/>
       <c r="Z41" s="298"/>
     </row>
-    <row r="42" spans="1:26" ht="14.25" customHeight="1">
+    <row r="42" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A42" s="34"/>
       <c r="B42" s="326"/>
       <c r="C42" s="323"/>
@@ -6230,7 +6229,7 @@
       <c r="Y42" s="246"/>
       <c r="Z42" s="298"/>
     </row>
-    <row r="43" spans="1:26" ht="14.25" customHeight="1">
+    <row r="43" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A43" s="34"/>
       <c r="B43" s="326"/>
       <c r="C43" s="323"/>
@@ -6266,7 +6265,7 @@
       <c r="Y43" s="246"/>
       <c r="Z43" s="298"/>
     </row>
-    <row r="44" spans="1:26" ht="14.25" customHeight="1">
+    <row r="44" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A44" s="34"/>
       <c r="B44" s="326"/>
       <c r="C44" s="323"/>
@@ -6302,7 +6301,7 @@
       <c r="Y44" s="246"/>
       <c r="Z44" s="298"/>
     </row>
-    <row r="45" spans="1:26" ht="14.25" customHeight="1">
+    <row r="45" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A45" s="34"/>
       <c r="B45" s="326"/>
       <c r="C45" s="323"/>
@@ -6338,7 +6337,7 @@
       <c r="Y45" s="246"/>
       <c r="Z45" s="298"/>
     </row>
-    <row r="46" spans="1:26" ht="14.25" customHeight="1">
+    <row r="46" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A46" s="35"/>
       <c r="B46" s="327"/>
       <c r="C46" s="324"/>
@@ -6376,7 +6375,7 @@
       <c r="Y46" s="299"/>
       <c r="Z46" s="300"/>
     </row>
-    <row r="47" spans="1:26" ht="14.25" customHeight="1">
+    <row r="47" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A47" s="50" t="s">
         <v>31</v>
       </c>
@@ -6414,7 +6413,7 @@
       </c>
       <c r="Z47" s="54"/>
     </row>
-    <row r="48" spans="1:26" ht="14.25" customHeight="1">
+    <row r="48" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A48" s="51"/>
       <c r="B48" s="22" t="s">
         <v>220</v>
@@ -6452,7 +6451,7 @@
       </c>
       <c r="Z48" s="184"/>
     </row>
-    <row r="49" spans="1:26" ht="14.25" customHeight="1">
+    <row r="49" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A49" s="51"/>
       <c r="B49" s="23" t="s">
         <v>242</v>
@@ -6490,7 +6489,7 @@
       </c>
       <c r="Z49" s="206"/>
     </row>
-    <row r="50" spans="1:26" ht="14.25" customHeight="1">
+    <row r="50" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A50" s="51"/>
       <c r="B50" s="23" t="s">
         <v>209</v>
@@ -6524,7 +6523,7 @@
       <c r="Y50" s="205"/>
       <c r="Z50" s="206"/>
     </row>
-    <row r="51" spans="1:26" ht="14.25" customHeight="1">
+    <row r="51" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A51" s="8" t="s">
         <v>27</v>
       </c>
@@ -6558,7 +6557,7 @@
       <c r="Y51" s="205"/>
       <c r="Z51" s="206"/>
     </row>
-    <row r="52" spans="1:26" ht="14.25" customHeight="1">
+    <row r="52" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A52" s="34" t="s">
         <v>313</v>
       </c>
@@ -6592,7 +6591,7 @@
       <c r="Y52" s="205"/>
       <c r="Z52" s="206"/>
     </row>
-    <row r="53" spans="1:26" ht="14.25" customHeight="1">
+    <row r="53" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A53" s="35"/>
       <c r="B53" s="22" t="s">
         <v>220</v>
@@ -6622,7 +6621,7 @@
       <c r="Y53" s="207"/>
       <c r="Z53" s="208"/>
     </row>
-    <row r="54" spans="1:26" ht="14.25" customHeight="1">
+    <row r="54" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A54" s="36" t="s">
         <v>39</v>
       </c>
@@ -6660,7 +6659,7 @@
       </c>
       <c r="Z54" s="54"/>
     </row>
-    <row r="55" spans="1:26" ht="14.25" customHeight="1">
+    <row r="55" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A55" s="209"/>
       <c r="B55" s="38" t="s">
         <v>17</v>
@@ -6700,7 +6699,7 @@
       </c>
       <c r="Z55" s="184"/>
     </row>
-    <row r="56" spans="1:26" ht="14.25" customHeight="1">
+    <row r="56" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A56" s="209"/>
       <c r="B56" s="39"/>
       <c r="C56" s="21" t="s">
@@ -6744,7 +6743,7 @@
       </c>
       <c r="Z56" s="206"/>
     </row>
-    <row r="57" spans="1:26" ht="14.25" customHeight="1">
+    <row r="57" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A57" s="209"/>
       <c r="B57" s="39"/>
       <c r="C57" s="21" t="s">
@@ -6784,7 +6783,7 @@
       <c r="Y57" s="205"/>
       <c r="Z57" s="206"/>
     </row>
-    <row r="58" spans="1:26" ht="14.25" customHeight="1">
+    <row r="58" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A58" s="209"/>
       <c r="B58" s="40"/>
       <c r="C58" s="24" t="s">
@@ -6818,7 +6817,7 @@
       <c r="Y58" s="205"/>
       <c r="Z58" s="206"/>
     </row>
-    <row r="59" spans="1:26" ht="14.25" customHeight="1">
+    <row r="59" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A59" s="6" t="s">
         <v>47</v>
       </c>
@@ -6856,7 +6855,7 @@
       <c r="Y59" s="205"/>
       <c r="Z59" s="206"/>
     </row>
-    <row r="60" spans="1:26" ht="14.25" customHeight="1">
+    <row r="60" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A60" s="34" t="s">
         <v>313</v>
       </c>
@@ -6892,7 +6891,7 @@
       <c r="Y60" s="205"/>
       <c r="Z60" s="206"/>
     </row>
-    <row r="61" spans="1:26" ht="14.25" customHeight="1">
+    <row r="61" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A61" s="34"/>
       <c r="B61" s="39"/>
       <c r="C61" s="21" t="s">
@@ -6930,7 +6929,7 @@
       <c r="Y61" s="205"/>
       <c r="Z61" s="206"/>
     </row>
-    <row r="62" spans="1:26" ht="14.25" customHeight="1">
+    <row r="62" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A62" s="35"/>
       <c r="B62" s="40"/>
       <c r="C62" s="21" t="s">
@@ -6968,7 +6967,7 @@
       <c r="Y62" s="207"/>
       <c r="Z62" s="208"/>
     </row>
-    <row r="63" spans="1:26" ht="14.25" customHeight="1">
+    <row r="63" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A63" s="36" t="s">
         <v>50</v>
       </c>
@@ -7006,7 +7005,7 @@
       </c>
       <c r="Z63" s="54"/>
     </row>
-    <row r="64" spans="1:26" ht="14.25" customHeight="1">
+    <row r="64" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A64" s="209"/>
       <c r="B64" s="22" t="s">
         <v>220</v>
@@ -7044,7 +7043,7 @@
       </c>
       <c r="Z64" s="184"/>
     </row>
-    <row r="65" spans="1:26" ht="14.25" customHeight="1">
+    <row r="65" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A65" s="209"/>
       <c r="B65" s="23"/>
       <c r="C65" s="154"/>
@@ -7078,7 +7077,7 @@
       </c>
       <c r="Z65" s="206"/>
     </row>
-    <row r="66" spans="1:26" ht="14.25" customHeight="1">
+    <row r="66" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A66" s="6" t="s">
         <v>27</v>
       </c>
@@ -7112,7 +7111,7 @@
       <c r="Y66" s="205"/>
       <c r="Z66" s="206"/>
     </row>
-    <row r="67" spans="1:26" ht="14.25" customHeight="1">
+    <row r="67" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A67" s="7" t="s">
         <v>313</v>
       </c>
@@ -7142,7 +7141,7 @@
       <c r="Y67" s="207"/>
       <c r="Z67" s="208"/>
     </row>
-    <row r="68" spans="1:26" ht="14.25" customHeight="1">
+    <row r="68" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A68" s="36" t="s">
         <v>56</v>
       </c>
@@ -7180,7 +7179,7 @@
       </c>
       <c r="Z68" s="54"/>
     </row>
-    <row r="69" spans="1:26" ht="14.25" customHeight="1">
+    <row r="69" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A69" s="209"/>
       <c r="B69" s="21" t="s">
         <v>215</v>
@@ -7218,7 +7217,7 @@
       </c>
       <c r="Z69" s="184"/>
     </row>
-    <row r="70" spans="1:26" ht="14.25" customHeight="1">
+    <row r="70" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A70" s="209"/>
       <c r="B70" s="21"/>
       <c r="C70" s="320"/>
@@ -7250,7 +7249,7 @@
       </c>
       <c r="Z70" s="243"/>
     </row>
-    <row r="71" spans="1:26" ht="14.25" customHeight="1">
+    <row r="71" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A71" s="209"/>
       <c r="B71" s="22" t="s">
         <v>220</v>
@@ -7284,7 +7283,7 @@
       <c r="Y71" s="242"/>
       <c r="Z71" s="243"/>
     </row>
-    <row r="72" spans="1:26" ht="14.25" customHeight="1">
+    <row r="72" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A72" s="209"/>
       <c r="B72" s="22" t="s">
         <v>220</v>
@@ -7318,7 +7317,7 @@
       <c r="Y72" s="242"/>
       <c r="Z72" s="243"/>
     </row>
-    <row r="73" spans="1:26" ht="14.25" customHeight="1">
+    <row r="73" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A73" s="209"/>
       <c r="B73" s="23" t="s">
         <v>216</v>
@@ -7352,7 +7351,7 @@
       <c r="Y73" s="242"/>
       <c r="Z73" s="243"/>
     </row>
-    <row r="74" spans="1:26" ht="14.25" customHeight="1">
+    <row r="74" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A74" s="209"/>
       <c r="B74" s="22" t="s">
         <v>220</v>
@@ -7384,7 +7383,7 @@
       <c r="Y74" s="242"/>
       <c r="Z74" s="243"/>
     </row>
-    <row r="75" spans="1:26" ht="14.25" customHeight="1">
+    <row r="75" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A75" s="6" t="s">
         <v>27</v>
       </c>
@@ -7418,7 +7417,7 @@
       <c r="Y75" s="242"/>
       <c r="Z75" s="243"/>
     </row>
-    <row r="76" spans="1:26" ht="14.25" customHeight="1">
+    <row r="76" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A76" s="7" t="s">
         <v>313</v>
       </c>
@@ -7452,7 +7451,7 @@
       <c r="Y76" s="244"/>
       <c r="Z76" s="245"/>
     </row>
-    <row r="77" spans="1:26" ht="14.25" customHeight="1">
+    <row r="77" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A77" s="9" t="s">
         <v>64</v>
       </c>
@@ -7490,7 +7489,7 @@
       </c>
       <c r="Z77" s="54"/>
     </row>
-    <row r="78" spans="1:26" ht="14.25" customHeight="1">
+    <row r="78" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A78" s="6" t="s">
         <v>68</v>
       </c>
@@ -7530,7 +7529,7 @@
       </c>
       <c r="Z78" s="184"/>
     </row>
-    <row r="79" spans="1:26" ht="14.25" customHeight="1">
+    <row r="79" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A79" s="6" t="s">
         <v>27</v>
       </c>
@@ -7568,7 +7567,7 @@
       </c>
       <c r="Z79" s="206"/>
     </row>
-    <row r="80" spans="1:26" ht="14.25" customHeight="1">
+    <row r="80" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A80" s="34" t="s">
         <v>313</v>
       </c>
@@ -7602,7 +7601,7 @@
       <c r="Y80" s="205"/>
       <c r="Z80" s="206"/>
     </row>
-    <row r="81" spans="1:26" ht="14.25" customHeight="1">
+    <row r="81" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A81" s="35"/>
       <c r="B81" s="22" t="s">
         <v>220</v>
@@ -7632,7 +7631,7 @@
       <c r="Y81" s="207"/>
       <c r="Z81" s="208"/>
     </row>
-    <row r="82" spans="1:26" ht="14.25" customHeight="1">
+    <row r="82" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A82" s="10" t="s">
         <v>72</v>
       </c>
@@ -7670,7 +7669,7 @@
       </c>
       <c r="Z82" s="54"/>
     </row>
-    <row r="83" spans="1:26" ht="14.25" customHeight="1">
+    <row r="83" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A83" s="8" t="s">
         <v>74</v>
       </c>
@@ -7712,7 +7711,7 @@
       </c>
       <c r="Z83" s="184"/>
     </row>
-    <row r="84" spans="1:26" ht="14.25" customHeight="1">
+    <row r="84" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A84" s="8" t="s">
         <v>76</v>
       </c>
@@ -7752,7 +7751,7 @@
       </c>
       <c r="Z84" s="206"/>
     </row>
-    <row r="85" spans="1:26" ht="14.25" customHeight="1">
+    <row r="85" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A85" s="8" t="s">
         <v>27</v>
       </c>
@@ -7786,7 +7785,7 @@
       <c r="Y85" s="205"/>
       <c r="Z85" s="206"/>
     </row>
-    <row r="86" spans="1:26" ht="14.25" customHeight="1">
+    <row r="86" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A86" s="34" t="s">
         <v>313</v>
       </c>
@@ -7822,7 +7821,7 @@
       <c r="Y86" s="205"/>
       <c r="Z86" s="206"/>
     </row>
-    <row r="87" spans="1:26" ht="14.25" customHeight="1">
+    <row r="87" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A87" s="34"/>
       <c r="B87" s="258"/>
       <c r="C87" s="23" t="s">
@@ -7854,7 +7853,7 @@
       <c r="Y87" s="205"/>
       <c r="Z87" s="206"/>
     </row>
-    <row r="88" spans="1:26" ht="14.25" customHeight="1">
+    <row r="88" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A88" s="34"/>
       <c r="B88" s="258"/>
       <c r="C88" s="23" t="s">
@@ -7886,7 +7885,7 @@
       <c r="Y88" s="205"/>
       <c r="Z88" s="206"/>
     </row>
-    <row r="89" spans="1:26" ht="14.25" customHeight="1">
+    <row r="89" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A89" s="34"/>
       <c r="B89" s="258"/>
       <c r="C89" s="23" t="s">
@@ -7918,7 +7917,7 @@
       <c r="Y89" s="205"/>
       <c r="Z89" s="206"/>
     </row>
-    <row r="90" spans="1:26" ht="14.25" customHeight="1">
+    <row r="90" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A90" s="34"/>
       <c r="B90" s="258"/>
       <c r="C90" s="23" t="s">
@@ -7950,7 +7949,7 @@
       <c r="Y90" s="205"/>
       <c r="Z90" s="206"/>
     </row>
-    <row r="91" spans="1:26" ht="14.25" customHeight="1">
+    <row r="91" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A91" s="34"/>
       <c r="B91" s="258"/>
       <c r="C91" s="23" t="s">
@@ -7982,7 +7981,7 @@
       <c r="Y91" s="205"/>
       <c r="Z91" s="206"/>
     </row>
-    <row r="92" spans="1:26" ht="14.25" customHeight="1">
+    <row r="92" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A92" s="34"/>
       <c r="B92" s="258"/>
       <c r="C92" s="23" t="s">
@@ -8014,7 +8013,7 @@
       <c r="Y92" s="205"/>
       <c r="Z92" s="206"/>
     </row>
-    <row r="93" spans="1:26" ht="14.25" customHeight="1">
+    <row r="93" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A93" s="34"/>
       <c r="B93" s="258"/>
       <c r="C93" s="23" t="s">
@@ -8046,7 +8045,7 @@
       <c r="Y93" s="205"/>
       <c r="Z93" s="206"/>
     </row>
-    <row r="94" spans="1:26" ht="14.25" customHeight="1">
+    <row r="94" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A94" s="34"/>
       <c r="B94" s="258"/>
       <c r="C94" s="23" t="s">
@@ -8078,7 +8077,7 @@
       <c r="Y94" s="205"/>
       <c r="Z94" s="206"/>
     </row>
-    <row r="95" spans="1:26" ht="14.25" customHeight="1">
+    <row r="95" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A95" s="34"/>
       <c r="B95" s="258"/>
       <c r="C95" s="21" t="s">
@@ -8110,7 +8109,7 @@
       <c r="Y95" s="205"/>
       <c r="Z95" s="206"/>
     </row>
-    <row r="96" spans="1:26" ht="14.25" customHeight="1">
+    <row r="96" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A96" s="34"/>
       <c r="B96" s="258"/>
       <c r="C96" s="21" t="s">
@@ -8142,7 +8141,7 @@
       <c r="Y96" s="205"/>
       <c r="Z96" s="206"/>
     </row>
-    <row r="97" spans="1:26" ht="14.25" customHeight="1">
+    <row r="97" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A97" s="34"/>
       <c r="B97" s="258"/>
       <c r="C97" s="21" t="s">
@@ -8174,7 +8173,7 @@
       <c r="Y97" s="205"/>
       <c r="Z97" s="206"/>
     </row>
-    <row r="98" spans="1:26" ht="14.25" customHeight="1">
+    <row r="98" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A98" s="35"/>
       <c r="B98" s="258"/>
       <c r="C98" s="21" t="s">
@@ -8206,7 +8205,7 @@
       <c r="Y98" s="207"/>
       <c r="Z98" s="208"/>
     </row>
-    <row r="99" spans="1:26" ht="14.25" customHeight="1">
+    <row r="99" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A99" s="275" t="s">
         <v>78</v>
       </c>
@@ -8236,7 +8235,7 @@
       <c r="Y99" s="276"/>
       <c r="Z99" s="277"/>
     </row>
-    <row r="100" spans="1:26" ht="14.25" customHeight="1">
+    <row r="100" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A100" s="267" t="s">
         <v>79</v>
       </c>
@@ -8266,7 +8265,7 @@
       <c r="Y100" s="268"/>
       <c r="Z100" s="269"/>
     </row>
-    <row r="101" spans="1:26" ht="14.25" customHeight="1">
+    <row r="101" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A101" s="267" t="s">
         <v>80</v>
       </c>
@@ -8296,7 +8295,7 @@
       <c r="Y101" s="268"/>
       <c r="Z101" s="269"/>
     </row>
-    <row r="102" spans="1:26" ht="14.25" customHeight="1">
+    <row r="102" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A102" s="282" t="s">
         <v>81</v>
       </c>
@@ -8326,7 +8325,7 @@
       <c r="Y102" s="283"/>
       <c r="Z102" s="284"/>
     </row>
-    <row r="103" spans="1:26" ht="14.25" customHeight="1">
+    <row r="103" spans="1:26" customFormat="false" ht="14.25" customHeight="1">
       <c r="A103" s="270" t="s">
         <v>154</v>
       </c>
@@ -8357,7 +8356,7 @@
       <c r="Z103" s="272"/>
     </row>
   </sheetData>
-  <mergeCells count="367">
+  <mergeCells count="371">
     <mergeCell ref="D37:G37"/>
     <mergeCell ref="D38:G38"/>
     <mergeCell ref="D27:G27"/>
@@ -8725,6 +8724,10 @@
     <mergeCell ref="H43:J43"/>
     <mergeCell ref="K43:L43"/>
     <mergeCell ref="M43:N43"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="D23:G23"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
